--- a/data/tags/אלבומים חדשים/sites/rotter/2026-03-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>עידן רייכל - הד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24457&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16:05</v>
+        <v>01:19</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>עידן רייכל - הד</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-27</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24461&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15:58</v>
+        <v>16:00</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>15:52</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>